--- a/Measurements/FAR_template_v3.xlsx
+++ b/Measurements/FAR_template_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\ManoEng\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337780B2-CDC9-4E65-8133-C08AE3BA92C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F26D64-8306-45B9-9992-399D2C0A51B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
   <sheets>
     <sheet name="FAI" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>Customer</t>
   </si>
@@ -146,9 +146,6 @@
     <t>Inspection Item</t>
   </si>
   <si>
-    <t>Requirement</t>
-  </si>
-  <si>
     <t>Sample Size</t>
   </si>
   <si>
@@ -171,6 +168,15 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>Types</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
+    <t>===========</t>
   </si>
 </sst>
 </file>
@@ -499,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -615,6 +621,12 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1797,7 +1809,7 @@
       </c>
       <c r="F1" s="34">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="G1" s="39" t="s">
         <v>21</v>
@@ -1813,7 +1825,9 @@
       <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="31" t="s">
+        <v>41</v>
+      </c>
       <c r="C2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1839,7 +1853,9 @@
       <c r="A3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="31" t="s">
+        <v>42</v>
+      </c>
       <c r="C3" s="20" t="s">
         <v>22</v>
       </c>
@@ -2200,7 +2216,7 @@
       </c>
       <c r="F1" s="34">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="G1" s="36" t="s">
         <v>30</v>
@@ -2210,7 +2226,10 @@
       <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="31" t="str">
+        <f>FAI!B2</f>
+        <v>-------------</v>
+      </c>
       <c r="C2" s="9" t="s">
         <v>17</v>
       </c>
@@ -2229,12 +2248,16 @@
       <c r="A3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="31" t="str">
+        <f>FAI!B3</f>
+        <v>===========</v>
+      </c>
       <c r="C3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>28</v>
+      <c r="D3" s="14" t="str">
+        <f>FAI!D3</f>
+        <v>Inch</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>5</v>
@@ -2247,22 +2270,22 @@
         <v>31</v>
       </c>
       <c r="B4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="E4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="F4" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="27" t="s">
-        <v>36</v>
-      </c>
       <c r="G4" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2270,16 +2293,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="6">
+        <v>36</v>
+      </c>
+      <c r="C5" s="40">
         <f>$D$2</f>
         <v>5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="41">
         <v>2</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="41">
         <f>C5-D5</f>
         <v>3</v>
       </c>
@@ -2294,14 +2317,14 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6">
+        <v>37</v>
+      </c>
+      <c r="C6" s="40">
         <f t="shared" ref="C6:C7" si="0">$D$2</f>
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
+      <c r="D6" s="41"/>
+      <c r="E6" s="41">
         <f t="shared" ref="E6:E7" si="1">C6-D6</f>
         <v>5</v>
       </c>
@@ -2316,14 +2339,14 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="6">
+        <v>38</v>
+      </c>
+      <c r="C7" s="40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
+      <c r="D7" s="41"/>
+      <c r="E7" s="41">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>

--- a/Measurements/FAR_template_v3.xlsx
+++ b/Measurements/FAR_template_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\ManoEng\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F26D64-8306-45B9-9992-399D2C0A51B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9737033D-97DE-403D-8ED9-8188288848CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
   <sheets>
     <sheet name="FAI" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">FAI!$A$5:$M$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Print Page 1'!$A$1:$Q$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">VI!$A$5:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">VI!$A$5:$G$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Customer</t>
   </si>
@@ -158,15 +158,6 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Burrs</t>
-  </si>
-  <si>
-    <t>Surface Finish</t>
-  </si>
-  <si>
-    <t>Coating</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -177,6 +168,30 @@
   </si>
   <si>
     <t>===========</t>
+  </si>
+  <si>
+    <t>Free from damage</t>
+  </si>
+  <si>
+    <t>Dent</t>
+  </si>
+  <si>
+    <t>Crack</t>
+  </si>
+  <si>
+    <t>Rusty</t>
+  </si>
+  <si>
+    <t>Scratch marks</t>
+  </si>
+  <si>
+    <t>Burr &amp; sharp edges</t>
+  </si>
+  <si>
+    <t>Hole shift</t>
+  </si>
+  <si>
+    <t>Plating</t>
   </si>
 </sst>
 </file>
@@ -505,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -610,23 +625,29 @@
     <xf numFmtId="1" fontId="9" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1809,9 +1830,9 @@
       </c>
       <c r="F1" s="34">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
-      </c>
-      <c r="G1" s="39" t="s">
+        <v>46141</v>
+      </c>
+      <c r="G1" s="38" t="s">
         <v>21</v>
       </c>
       <c r="H1" s="17"/>
@@ -1826,7 +1847,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>17</v>
@@ -1840,7 +1861,7 @@
       <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="37"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="17"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -1854,7 +1875,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>22</v>
@@ -1866,7 +1887,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="38"/>
+      <c r="G3" s="40"/>
       <c r="H3" s="18"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
@@ -2189,7 +2210,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="1" customWidth="1"/>
@@ -2216,9 +2237,9 @@
       </c>
       <c r="F1" s="34">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
-      </c>
-      <c r="G1" s="36" t="s">
+        <v>46141</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2242,7 +2263,7 @@
       <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="37"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
@@ -2263,14 +2284,14 @@
         <v>5</v>
       </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="38"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>32</v>
@@ -2285,7 +2306,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2293,16 +2314,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="40">
+        <v>40</v>
+      </c>
+      <c r="C5" s="36">
         <f>$D$2</f>
         <v>5</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="37">
         <v>2</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="37">
         <f>C5-D5</f>
         <v>3</v>
       </c>
@@ -2317,19 +2338,19 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="40">
-        <f t="shared" ref="C6:C7" si="0">$D$2</f>
+        <v>41</v>
+      </c>
+      <c r="C6" s="36">
+        <f t="shared" ref="C6:C12" si="0">$D$2</f>
         <v>5</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41">
-        <f t="shared" ref="E6:E7" si="1">C6-D6</f>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37">
+        <f t="shared" ref="E6:E12" si="1">C6-D6</f>
         <v>5</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f t="shared" ref="F6:F7" si="2">IF(D6=0, "PASS", "FAIL")</f>
+        <f t="shared" ref="F6:F12" si="2">IF(D6=0, "PASS", "FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="G6" s="3"/>
@@ -2339,14 +2360,14 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="40">
+        <v>42</v>
+      </c>
+      <c r="C7" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41">
+      <c r="D7" s="37"/>
+      <c r="E7" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2355,6 +2376,116 @@
         <v>PASS</v>
       </c>
       <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="36">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PASS</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>5</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="36">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PASS</v>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="36">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PASS</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="36">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PASS</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="36">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PASS</v>
+      </c>
+      <c r="G12" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
